--- a/SFN/Trust Behavioral Analysis/IOS/iosXageFS.xlsx
+++ b/SFN/Trust Behavioral Analysis/IOS/iosXageFS.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/Trust Behavioral Analysis/IOS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD95CE0B-42D7-C947-8654-4EAA2A26ABB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9CD8BC9-05D1-C848-A467-96A5CB57501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{8DC24A9A-5B2A-AD43-8B9B-7B1381C07E0D}"/>
+    <workbookView xWindow="3280" yWindow="500" windowWidth="25520" windowHeight="16120" xr2:uid="{8DC24A9A-5B2A-AD43-8B9B-7B1381C07E0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,15 +36,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>age</t>
   </si>
   <si>
-    <t>iosF_S</t>
+    <t>ios_friend_score</t>
   </si>
   <si>
-    <t>iosF_C</t>
+    <t>ios_computer_score</t>
+  </si>
+  <si>
+    <t>ios_stranger_score</t>
+  </si>
+  <si>
+    <t>fc</t>
+  </si>
+  <si>
+    <t>fs</t>
   </si>
 </sst>
 </file>
@@ -396,10 +405,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0817B071-EC23-AC4A-B553-B9F2823149D3}">
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -407,142 +416,283 @@
         <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
         <v>62.96</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E2">
+        <f>A2-B2</f>
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <f>A2-C2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
         <v>31.95</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E3">
+        <f t="shared" ref="E3:E65" si="0">A3-B3</f>
+        <v>3</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F65" si="1">A3-C3</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
         <v>44.21</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>35.94</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="C5">
-        <v>35.94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>68.64</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C6">
-        <v>68.64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>62.04</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
         <v>27.9</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4</v>
       </c>
       <c r="B9">
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>41.91</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C9">
-        <v>41.91</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
         <v>67.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
         <v>69.16</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E11">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5</v>
       </c>
       <c r="B12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
         <v>28.86</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E12">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5</v>
       </c>
       <c r="B13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
         <v>28.31</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E13">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2</v>
       </c>
@@ -550,208 +700,417 @@
         <v>1</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
         <v>70.459999999999994</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E14">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>2</v>
       </c>
       <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>48.03</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C15">
-        <v>48.03</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>6</v>
       </c>
       <c r="B16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
         <v>49.64</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E16">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>7</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
         <v>63.33</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E17">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>5</v>
       </c>
       <c r="B18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
         <v>34.869999999999997</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E18">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
         <v>56.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E19">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
         <v>27.27</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E20">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>7</v>
       </c>
       <c r="B21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C21">
+        <v>4</v>
+      </c>
+      <c r="D21">
         <v>69.22</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>5</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
         <v>22.4</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E22">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
       <c r="B23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
         <v>29.07</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E23">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>6</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24">
         <v>73.400000000000006</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>7</v>
       </c>
       <c r="B25">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
         <v>26.81</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E25">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>6</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
         <v>71.83</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E26">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
         <v>31.73</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E27">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>7</v>
       </c>
       <c r="B28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
         <v>44.68</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E28">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29">
+        <v>4</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>31.9</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="C29">
-        <v>31.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>6</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
         <v>69.41</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E30">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
       <c r="B31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C31">
+        <v>2</v>
+      </c>
+      <c r="D31">
         <v>24.59</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E31">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>6</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
         <v>63.8</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E32">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2</v>
       </c>
@@ -759,109 +1118,219 @@
         <v>1</v>
       </c>
       <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
         <v>70.05</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E33">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>7</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C34">
+        <v>5</v>
+      </c>
+      <c r="D34">
         <v>21.43</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E34">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4</v>
       </c>
       <c r="B35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
         <v>58.98</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E35">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C36">
+        <v>1</v>
+      </c>
+      <c r="D36">
         <v>62.39</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E36">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>7</v>
       </c>
       <c r="B37">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>50.64</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>7</v>
       </c>
       <c r="B38">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38">
         <v>22.07</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E38">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>37.369999999999997</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
         <v>48.6</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E40">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C41">
+        <v>5</v>
+      </c>
+      <c r="D41">
         <v>33.200000000000003</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E41">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
         <v>33.369999999999997</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E42">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2</v>
       </c>
@@ -869,10 +1338,21 @@
         <v>1</v>
       </c>
       <c r="C43">
+        <v>1</v>
+      </c>
+      <c r="D43">
         <v>34.43</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E43">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2</v>
       </c>
@@ -880,304 +1360,590 @@
         <v>1</v>
       </c>
       <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>56.16</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>58.27</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46">
+        <v>6</v>
+      </c>
+      <c r="B46">
+        <v>2</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
+      </c>
+      <c r="D46">
+        <v>23.61</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47">
+        <v>6</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+      <c r="D47">
+        <v>27.02</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>69.13</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49">
+        <v>7</v>
+      </c>
+      <c r="B49">
+        <v>3</v>
+      </c>
+      <c r="C49">
+        <v>4</v>
+      </c>
+      <c r="D49">
+        <v>28.3</v>
+      </c>
+      <c r="E49">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50">
+        <v>6</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>33.44</v>
+      </c>
+      <c r="E50">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51">
+        <v>5</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>21.7</v>
+      </c>
+      <c r="E51">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45">
-        <v>6</v>
-      </c>
-      <c r="B45">
-        <v>5</v>
-      </c>
-      <c r="C45">
-        <v>58.27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46">
-        <v>6</v>
-      </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-      <c r="C46">
-        <v>23.61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47">
-        <v>6</v>
-      </c>
-      <c r="B47">
-        <v>5</v>
-      </c>
-      <c r="C47">
-        <v>27.02</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48">
-        <v>0</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
-        <v>71.53</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49">
-        <v>4</v>
-      </c>
-      <c r="B49">
-        <v>3</v>
-      </c>
-      <c r="C49">
-        <v>69.13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50">
-        <v>4</v>
-      </c>
-      <c r="B50">
-        <v>4</v>
-      </c>
-      <c r="C50">
-        <v>28.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51">
-        <v>6</v>
-      </c>
-      <c r="B51">
-        <v>4</v>
-      </c>
-      <c r="C51">
-        <v>33.44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>21.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>36.93</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>36.93</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D53">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+      <c r="D54">
+        <v>25.51</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>7</v>
       </c>
-      <c r="B54">
-        <v>4</v>
-      </c>
-      <c r="C54">
-        <v>33.299999999999997</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55">
-        <v>1</v>
-      </c>
       <c r="B55">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C55">
-        <v>25.51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>64.52</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>64.52</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="D56">
+        <v>46.3</v>
+      </c>
+      <c r="E56">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D57">
+        <v>38.36</v>
+      </c>
+      <c r="E57">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58">
-        <v>38.36</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>37.53</v>
+      </c>
+      <c r="E58">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59">
-        <v>37.53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>51.18</v>
+      </c>
+      <c r="E59">
+        <f t="shared" si="0"/>
+        <v>-1</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B60">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>51.18</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>61.23</v>
+      </c>
+      <c r="E60">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>4</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>61.23</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D61">
+        <v>39.69</v>
+      </c>
+      <c r="E61">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
-        <v>39.69</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>26.85</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>26.85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="D63">
+        <v>34.53</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>34.53</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+      <c r="D64">
+        <v>42.69</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>42.69</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>21.66</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C66">
-        <v>21.66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D66">
+        <v>25.5</v>
+      </c>
+      <c r="E66">
+        <f t="shared" ref="E66:E70" si="2">A66-B66</f>
+        <v>1</v>
+      </c>
+      <c r="F66">
+        <f t="shared" ref="F66:F70" si="3">A66-C66</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>25.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D67">
+        <v>26.99</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B68">
         <v>4</v>
       </c>
       <c r="C68">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="D68">
+        <v>58.05</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>58.05</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="D69">
+        <v>68.77</v>
+      </c>
+      <c r="E69">
+        <f t="shared" si="2"/>
+        <v>5</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70">
-        <v>68.77</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71">
-        <v>4</v>
-      </c>
-      <c r="B71">
-        <v>3</v>
-      </c>
-      <c r="C71">
+        <v>3</v>
+      </c>
+      <c r="D70">
         <v>62.91</v>
+      </c>
+      <c r="E70">
+        <f t="shared" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="3"/>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
